--- a/data/weekly_report.xlsx
+++ b/data/weekly_report.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1262"/>
+  <dimension ref="A1:I1297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41873,7 +41873,7 @@
         </is>
       </c>
       <c r="G1256" s="1" t="n">
-        <v>46276.63760464759</v>
+        <v>46276.63760465278</v>
       </c>
       <c r="H1256" t="n">
         <v>41.605</v>
@@ -41906,7 +41906,7 @@
         </is>
       </c>
       <c r="G1257" s="1" t="n">
-        <v>46276.63760464759</v>
+        <v>46276.63760465278</v>
       </c>
       <c r="H1257" t="n">
         <v>5526</v>
@@ -41939,7 +41939,7 @@
         </is>
       </c>
       <c r="G1258" s="1" t="n">
-        <v>46276.63760464759</v>
+        <v>46276.63760465278</v>
       </c>
       <c r="H1258" t="n">
         <v>348.7</v>
@@ -41972,7 +41972,7 @@
         </is>
       </c>
       <c r="G1259" s="1" t="n">
-        <v>46276.63760464759</v>
+        <v>46276.63760465278</v>
       </c>
       <c r="H1259" t="n">
         <v>40.27</v>
@@ -42005,7 +42005,7 @@
         </is>
       </c>
       <c r="G1260" s="1" t="n">
-        <v>46276.63760464759</v>
+        <v>46276.63760465278</v>
       </c>
       <c r="H1260" t="n">
         <v>84.59999999999999</v>
@@ -42038,7 +42038,7 @@
         </is>
       </c>
       <c r="G1261" s="1" t="n">
-        <v>46276.63760464759</v>
+        <v>46276.63760465278</v>
       </c>
       <c r="H1261" t="n">
         <v>71.76000000000001</v>
@@ -42053,31 +42053,1186 @@
       </c>
       <c r="B1262" t="inlineStr">
         <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1262" t="n">
+        <v>5506</v>
+      </c>
+      <c r="D1262" t="n">
+        <v>5781.3</v>
+      </c>
+      <c r="E1262" t="n">
+        <v>5230.7</v>
+      </c>
+      <c r="F1262" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1262" s="1" t="n">
+        <v>46279.7219420949</v>
+      </c>
+      <c r="H1262" t="n">
+        <v>5498</v>
+      </c>
+      <c r="I1262" t="n">
+        <v>0.1452960406828914</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
           <t>ALRS</t>
         </is>
       </c>
-      <c r="C1262" t="n">
+      <c r="C1263" t="n">
         <v>21.42</v>
       </c>
-      <c r="D1262" t="n">
+      <c r="D1263" t="n">
         <v>22.491</v>
       </c>
-      <c r="E1262" t="n">
+      <c r="E1263" t="n">
         <v>20.349</v>
       </c>
-      <c r="F1262" t="inlineStr">
-        <is>
-          <t>Sell</t>
-        </is>
-      </c>
-      <c r="G1262" s="1" t="n">
-        <v>46276.63760464759</v>
-      </c>
-      <c r="H1262" t="n">
+      <c r="F1263" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1263" s="1" t="n">
+        <v>46276.63760465278</v>
+      </c>
+      <c r="H1263" t="n">
         <v>20.349</v>
       </c>
-      <c r="I1262" t="n">
+      <c r="I1263" t="n">
         <v>5.000000000000006</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1264" t="n">
+        <v>23.015</v>
+      </c>
+      <c r="D1264" t="n">
+        <v>24.16575</v>
+      </c>
+      <c r="E1264" t="n">
+        <v>21.86425</v>
+      </c>
+      <c r="F1264" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1264" s="1" t="n">
+        <v>46279.7219420949</v>
+      </c>
+      <c r="H1264" t="n">
+        <v>22.17</v>
+      </c>
+      <c r="I1264" t="n">
+        <v>3.671518574842489</v>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>RTKM</t>
+        </is>
+      </c>
+      <c r="C1265" t="n">
+        <v>41.66</v>
+      </c>
+      <c r="D1265" t="n">
+        <v>43.74299999999999</v>
+      </c>
+      <c r="E1265" t="n">
+        <v>39.577</v>
+      </c>
+      <c r="F1265" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1265" s="1" t="n">
+        <v>46279.7219420949</v>
+      </c>
+      <c r="H1265" t="n">
+        <v>39.82</v>
+      </c>
+      <c r="I1265" t="n">
+        <v>4.416706673067682</v>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>NLMK</t>
+        </is>
+      </c>
+      <c r="C1266" t="n">
+        <v>73.92</v>
+      </c>
+      <c r="D1266" t="n">
+        <v>77.616</v>
+      </c>
+      <c r="E1266" t="n">
+        <v>70.224</v>
+      </c>
+      <c r="F1266" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1266" s="1" t="n">
+        <v>46279.7219420949</v>
+      </c>
+      <c r="H1266" t="n">
+        <v>72.42</v>
+      </c>
+      <c r="I1266" t="n">
+        <v>2.029220779220779</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1267" t="n">
+        <v>5466</v>
+      </c>
+      <c r="D1267" t="n">
+        <v>5739.3</v>
+      </c>
+      <c r="E1267" t="n">
+        <v>5192.7</v>
+      </c>
+      <c r="F1267" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1267" s="1" t="n">
+        <v>46279.7219420949</v>
+      </c>
+      <c r="H1267" t="n">
+        <v>5498</v>
+      </c>
+      <c r="I1267" t="n">
+        <v>-0.5854372484449323</v>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1268" t="n">
+        <v>5186.5</v>
+      </c>
+      <c r="D1268" t="n">
+        <v>5445.825</v>
+      </c>
+      <c r="E1268" t="n">
+        <v>4927.175</v>
+      </c>
+      <c r="F1268" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1268" s="1" t="n">
+        <v>46279.7219420949</v>
+      </c>
+      <c r="H1268" t="n">
+        <v>5410.5</v>
+      </c>
+      <c r="I1268" t="n">
+        <v>-4.318904849127542</v>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1269" t="n">
+        <v>20.63</v>
+      </c>
+      <c r="D1269" t="n">
+        <v>21.6615</v>
+      </c>
+      <c r="E1269" t="n">
+        <v>19.5985</v>
+      </c>
+      <c r="F1269" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1269" s="1" t="n">
+        <v>46279.7219420949</v>
+      </c>
+      <c r="H1269" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="I1269" t="n">
+        <v>3.538536112457588</v>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1270" t="n">
+        <v>22.525</v>
+      </c>
+      <c r="D1270" t="n">
+        <v>23.65125</v>
+      </c>
+      <c r="E1270" t="n">
+        <v>21.39875</v>
+      </c>
+      <c r="F1270" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1270" s="1" t="n">
+        <v>46279.7219420949</v>
+      </c>
+      <c r="H1270" t="n">
+        <v>22.17</v>
+      </c>
+      <c r="I1270" t="n">
+        <v>1.576026637069909</v>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>TRMK</t>
+        </is>
+      </c>
+      <c r="C1271" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="D1271" t="n">
+        <v>62.79</v>
+      </c>
+      <c r="E1271" t="n">
+        <v>56.81</v>
+      </c>
+      <c r="F1271" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1271" s="1" t="n">
+        <v>46279.7219420949</v>
+      </c>
+      <c r="H1271" t="n">
+        <v>59.24</v>
+      </c>
+      <c r="I1271" t="n">
+        <v>0.9364548494983197</v>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>MGNT</t>
+        </is>
+      </c>
+      <c r="C1272" t="n">
+        <v>1636.5</v>
+      </c>
+      <c r="D1272" t="n">
+        <v>1554.675</v>
+      </c>
+      <c r="E1272" t="n">
+        <v>1767.42</v>
+      </c>
+      <c r="F1272" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1272" s="1" t="n">
+        <v>46279.7219420949</v>
+      </c>
+      <c r="H1272" t="n">
+        <v>1599</v>
+      </c>
+      <c r="I1272" t="n">
+        <v>-2.29147571035747</v>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>TATN</t>
+        </is>
+      </c>
+      <c r="C1273" t="n">
+        <v>629.4</v>
+      </c>
+      <c r="D1273" t="n">
+        <v>597.9299999999999</v>
+      </c>
+      <c r="E1273" t="n">
+        <v>679.7520000000001</v>
+      </c>
+      <c r="F1273" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1273" s="1" t="n">
+        <v>46279.7219420949</v>
+      </c>
+      <c r="H1273" t="n">
+        <v>632.5</v>
+      </c>
+      <c r="I1273" t="n">
+        <v>0.4925325707022597</v>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>ENPG</t>
+        </is>
+      </c>
+      <c r="C1274" t="n">
+        <v>310.1</v>
+      </c>
+      <c r="D1274" t="n">
+        <v>294.595</v>
+      </c>
+      <c r="E1274" t="n">
+        <v>334.9080000000001</v>
+      </c>
+      <c r="F1274" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1274" s="1" t="n">
+        <v>46279.7219420949</v>
+      </c>
+      <c r="H1274" t="n">
+        <v>314.6</v>
+      </c>
+      <c r="I1274" t="n">
+        <v>1.45114479200258</v>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1275" t="n">
+        <v>22.81</v>
+      </c>
+      <c r="D1275" t="n">
+        <v>21.6695</v>
+      </c>
+      <c r="E1275" t="n">
+        <v>24.6348</v>
+      </c>
+      <c r="F1275" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1275" s="1" t="n">
+        <v>46279.7219420949</v>
+      </c>
+      <c r="H1275" t="n">
+        <v>22.17</v>
+      </c>
+      <c r="I1275" t="n">
+        <v>-2.805786935554568</v>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>SBER</t>
+        </is>
+      </c>
+      <c r="C1276" t="n">
+        <v>285</v>
+      </c>
+      <c r="D1276" t="n">
+        <v>270.75</v>
+      </c>
+      <c r="E1276" t="n">
+        <v>307.8</v>
+      </c>
+      <c r="F1276" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1276" s="1" t="n">
+        <v>46279.7219420949</v>
+      </c>
+      <c r="H1276" t="n">
+        <v>285.66</v>
+      </c>
+      <c r="I1276" t="n">
+        <v>0.2315789473684298</v>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>AFLT</t>
+        </is>
+      </c>
+      <c r="C1277" t="n">
+        <v>33</v>
+      </c>
+      <c r="D1277" t="n">
+        <v>34.65</v>
+      </c>
+      <c r="E1277" t="n">
+        <v>31.35</v>
+      </c>
+      <c r="F1277" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1277" s="1" t="n">
+        <v>46279.7219420949</v>
+      </c>
+      <c r="H1277" t="n">
+        <v>33.06</v>
+      </c>
+      <c r="I1277" t="n">
+        <v>-0.1818181818181887</v>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>RUAL</t>
+        </is>
+      </c>
+      <c r="C1278" t="n">
+        <v>26.69</v>
+      </c>
+      <c r="D1278" t="n">
+        <v>28.0245</v>
+      </c>
+      <c r="E1278" t="n">
+        <v>25.3555</v>
+      </c>
+      <c r="F1278" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1278" s="1" t="n">
+        <v>46279.7219420949</v>
+      </c>
+      <c r="H1278" t="n">
+        <v>25.54</v>
+      </c>
+      <c r="I1278" t="n">
+        <v>4.308729861371308</v>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>AFKS</t>
+        </is>
+      </c>
+      <c r="C1279" t="n">
+        <v>7.603</v>
+      </c>
+      <c r="D1279" t="n">
+        <v>7.98315</v>
+      </c>
+      <c r="E1279" t="n">
+        <v>7.222849999999999</v>
+      </c>
+      <c r="F1279" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1279" s="1" t="n">
+        <v>46279.7219420949</v>
+      </c>
+      <c r="H1279" t="n">
+        <v>7.304</v>
+      </c>
+      <c r="I1279" t="n">
+        <v>3.93265816125213</v>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>GMKN</t>
+        </is>
+      </c>
+      <c r="C1280" t="n">
+        <v>132.34</v>
+      </c>
+      <c r="D1280" t="n">
+        <v>138.957</v>
+      </c>
+      <c r="E1280" t="n">
+        <v>125.723</v>
+      </c>
+      <c r="F1280" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1280" s="1" t="n">
+        <v>46279.7219420949</v>
+      </c>
+      <c r="H1280" t="n">
+        <v>128.42</v>
+      </c>
+      <c r="I1280" t="n">
+        <v>2.962067402146</v>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>OZON</t>
+        </is>
+      </c>
+      <c r="C1281" t="n">
+        <v>2569.5</v>
+      </c>
+      <c r="D1281" t="n">
+        <v>2697.975</v>
+      </c>
+      <c r="E1281" t="n">
+        <v>2441.025</v>
+      </c>
+      <c r="F1281" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1281" s="1" t="n">
+        <v>46279.7219420949</v>
+      </c>
+      <c r="H1281" t="n">
+        <v>2649.5</v>
+      </c>
+      <c r="I1281" t="n">
+        <v>-3.11344619575793</v>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1282" t="n">
+        <v>5542</v>
+      </c>
+      <c r="D1282" t="n">
+        <v>5819.1</v>
+      </c>
+      <c r="E1282" t="n">
+        <v>5264.9</v>
+      </c>
+      <c r="F1282" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1282" s="1" t="n">
+        <v>46281.65458431713</v>
+      </c>
+      <c r="H1282" t="n">
+        <v>5264.9</v>
+      </c>
+      <c r="I1282" t="n">
+        <v>5.000000000000006</v>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>RTKM</t>
+        </is>
+      </c>
+      <c r="C1283" t="n">
+        <v>40.11</v>
+      </c>
+      <c r="D1283" t="n">
+        <v>42.1155</v>
+      </c>
+      <c r="E1283" t="n">
+        <v>38.10449999999999</v>
+      </c>
+      <c r="F1283" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1283" s="1" t="n">
+        <v>46282.65388032408</v>
+      </c>
+      <c r="H1283" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="I1283" t="n">
+        <v>2.592869608576413</v>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1284" t="n">
+        <v>5285</v>
+      </c>
+      <c r="D1284" t="n">
+        <v>5549.25</v>
+      </c>
+      <c r="E1284" t="n">
+        <v>5020.75</v>
+      </c>
+      <c r="F1284" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1284" s="1" t="n">
+        <v>46280.65773967592</v>
+      </c>
+      <c r="H1284" t="n">
+        <v>5549.25</v>
+      </c>
+      <c r="I1284" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>RNFT</t>
+        </is>
+      </c>
+      <c r="C1285" t="n">
+        <v>84.65000000000001</v>
+      </c>
+      <c r="D1285" t="n">
+        <v>88.88250000000001</v>
+      </c>
+      <c r="E1285" t="n">
+        <v>80.4175</v>
+      </c>
+      <c r="F1285" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1285" s="1" t="n">
+        <v>46282.65388032408</v>
+      </c>
+      <c r="H1285" t="n">
+        <v>83.45</v>
+      </c>
+      <c r="I1285" t="n">
+        <v>1.417601890135857</v>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>HYDR</t>
+        </is>
+      </c>
+      <c r="C1286" t="n">
+        <v>0.3784</v>
+      </c>
+      <c r="D1286" t="n">
+        <v>0.39732</v>
+      </c>
+      <c r="E1286" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="F1286" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1286" s="1" t="n">
+        <v>46282.65388032408</v>
+      </c>
+      <c r="H1286" t="n">
+        <v>0.3716</v>
+      </c>
+      <c r="I1286" t="n">
+        <v>1.7970401691332</v>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>VTBR</t>
+        </is>
+      </c>
+      <c r="C1287" t="n">
+        <v>52.39</v>
+      </c>
+      <c r="D1287" t="n">
+        <v>49.7705</v>
+      </c>
+      <c r="E1287" t="n">
+        <v>56.5812</v>
+      </c>
+      <c r="F1287" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1287" s="1" t="n">
+        <v>46282.65388032408</v>
+      </c>
+      <c r="H1287" t="n">
+        <v>49.7705</v>
+      </c>
+      <c r="I1287" t="n">
+        <v>-5.000000000000004</v>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>SNGSP</t>
+        </is>
+      </c>
+      <c r="C1288" t="n">
+        <v>42.58</v>
+      </c>
+      <c r="D1288" t="n">
+        <v>40.45099999999999</v>
+      </c>
+      <c r="E1288" t="n">
+        <v>45.9864</v>
+      </c>
+      <c r="F1288" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1288" s="1" t="n">
+        <v>46283.63822962082</v>
+      </c>
+      <c r="H1288" t="n">
+        <v>40.53</v>
+      </c>
+      <c r="I1288" t="n">
+        <v>-4.814466885861901</v>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>TATN</t>
+        </is>
+      </c>
+      <c r="C1289" t="n">
+        <v>639</v>
+      </c>
+      <c r="D1289" t="n">
+        <v>607.05</v>
+      </c>
+      <c r="E1289" t="n">
+        <v>690.12</v>
+      </c>
+      <c r="F1289" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1289" s="1" t="n">
+        <v>46283.63822962082</v>
+      </c>
+      <c r="H1289" t="n">
+        <v>617.8</v>
+      </c>
+      <c r="I1289" t="n">
+        <v>-3.31768388106417</v>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>ROSN</t>
+        </is>
+      </c>
+      <c r="C1290" t="n">
+        <v>371</v>
+      </c>
+      <c r="D1290" t="n">
+        <v>352.45</v>
+      </c>
+      <c r="E1290" t="n">
+        <v>400.68</v>
+      </c>
+      <c r="F1290" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1290" s="1" t="n">
+        <v>46282.65388032408</v>
+      </c>
+      <c r="H1290" t="n">
+        <v>352.45</v>
+      </c>
+      <c r="I1290" t="n">
+        <v>-5.000000000000003</v>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>HYDR</t>
+        </is>
+      </c>
+      <c r="C1291" t="n">
+        <v>0.3919</v>
+      </c>
+      <c r="D1291" t="n">
+        <v>0.4114950000000001</v>
+      </c>
+      <c r="E1291" t="n">
+        <v>0.372305</v>
+      </c>
+      <c r="F1291" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1291" s="1" t="n">
+        <v>46282.65388032408</v>
+      </c>
+      <c r="H1291" t="n">
+        <v>0.372305</v>
+      </c>
+      <c r="I1291" t="n">
+        <v>5.000000000000007</v>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1292" t="n">
+        <v>5532</v>
+      </c>
+      <c r="D1292" t="n">
+        <v>5808.6</v>
+      </c>
+      <c r="E1292" t="n">
+        <v>5255.4</v>
+      </c>
+      <c r="F1292" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1292" s="1" t="n">
+        <v>46282.65388032408</v>
+      </c>
+      <c r="H1292" t="n">
+        <v>5255.4</v>
+      </c>
+      <c r="I1292" t="n">
+        <v>5.000000000000006</v>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1293" t="n">
+        <v>5478</v>
+      </c>
+      <c r="D1293" t="n">
+        <v>5751.900000000001</v>
+      </c>
+      <c r="E1293" t="n">
+        <v>5204.099999999999</v>
+      </c>
+      <c r="F1293" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1293" s="1" t="n">
+        <v>46282.65388032408</v>
+      </c>
+      <c r="H1293" t="n">
+        <v>5204.099999999999</v>
+      </c>
+      <c r="I1293" t="n">
+        <v>5.00000000000001</v>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>AFLT</t>
+        </is>
+      </c>
+      <c r="C1294" t="n">
+        <v>33.22</v>
+      </c>
+      <c r="D1294" t="n">
+        <v>34.881</v>
+      </c>
+      <c r="E1294" t="n">
+        <v>31.559</v>
+      </c>
+      <c r="F1294" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1294" s="1" t="n">
+        <v>46283.63822962082</v>
+      </c>
+      <c r="H1294" t="n">
+        <v>32.13</v>
+      </c>
+      <c r="I1294" t="n">
+        <v>3.281155930162542</v>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>ENPG</t>
+        </is>
+      </c>
+      <c r="C1295" t="n">
+        <v>318.9</v>
+      </c>
+      <c r="D1295" t="n">
+        <v>334.845</v>
+      </c>
+      <c r="E1295" t="n">
+        <v>302.955</v>
+      </c>
+      <c r="F1295" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1295" s="1" t="n">
+        <v>46282.65388032408</v>
+      </c>
+      <c r="H1295" t="n">
+        <v>302.955</v>
+      </c>
+      <c r="I1295" t="n">
+        <v>4.999999999999998</v>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>MTSS</t>
+        </is>
+      </c>
+      <c r="C1296" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="D1296" t="n">
+        <v>209.895</v>
+      </c>
+      <c r="E1296" t="n">
+        <v>189.905</v>
+      </c>
+      <c r="F1296" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1296" s="1" t="n">
+        <v>46282.65388032408</v>
+      </c>
+      <c r="H1296" t="n">
+        <v>189.905</v>
+      </c>
+      <c r="I1296" t="n">
+        <v>5.000000000000003</v>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>MTSS</t>
+        </is>
+      </c>
+      <c r="C1297" t="n">
+        <v>185.15</v>
+      </c>
+      <c r="D1297" t="n">
+        <v>194.4075</v>
+      </c>
+      <c r="E1297" t="n">
+        <v>175.8925</v>
+      </c>
+      <c r="F1297" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1297" s="1" t="n">
+        <v>46283.63822962082</v>
+      </c>
+      <c r="H1297" t="n">
+        <v>175.8925</v>
+      </c>
+      <c r="I1297" t="n">
+        <v>4.999999999999996</v>
       </c>
     </row>
   </sheetData>

--- a/data/weekly_report.xlsx
+++ b/data/weekly_report.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1297"/>
+  <dimension ref="A1:I1323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42929,7 +42929,7 @@
         </is>
       </c>
       <c r="G1288" s="1" t="n">
-        <v>46283.63822962082</v>
+        <v>46283.63822961805</v>
       </c>
       <c r="H1288" t="n">
         <v>40.53</v>
@@ -42962,7 +42962,7 @@
         </is>
       </c>
       <c r="G1289" s="1" t="n">
-        <v>46283.63822962082</v>
+        <v>46283.63822961805</v>
       </c>
       <c r="H1289" t="n">
         <v>617.8</v>
@@ -43127,7 +43127,7 @@
         </is>
       </c>
       <c r="G1294" s="1" t="n">
-        <v>46283.63822962082</v>
+        <v>46283.63822961805</v>
       </c>
       <c r="H1294" t="n">
         <v>32.13</v>
@@ -43175,17 +43175,17 @@
       </c>
       <c r="B1296" t="inlineStr">
         <is>
-          <t>MTSS</t>
+          <t>PHOR</t>
         </is>
       </c>
       <c r="C1296" t="n">
-        <v>199.9</v>
+        <v>5319</v>
       </c>
       <c r="D1296" t="n">
-        <v>209.895</v>
+        <v>5584.95</v>
       </c>
       <c r="E1296" t="n">
-        <v>189.905</v>
+        <v>5053.05</v>
       </c>
       <c r="F1296" t="inlineStr">
         <is>
@@ -43193,46 +43193,904 @@
         </is>
       </c>
       <c r="G1296" s="1" t="n">
-        <v>46282.65388032408</v>
+        <v>46286.72618741898</v>
       </c>
       <c r="H1296" t="n">
-        <v>189.905</v>
+        <v>5022</v>
       </c>
       <c r="I1296" t="n">
-        <v>5.000000000000003</v>
+        <v>5.583756345177665</v>
       </c>
     </row>
     <row r="1297">
       <c r="A1297" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1297" t="n">
+        <v>21.705</v>
+      </c>
+      <c r="D1297" t="n">
+        <v>22.79025</v>
+      </c>
+      <c r="E1297" t="n">
+        <v>20.61975</v>
+      </c>
+      <c r="F1297" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1297" s="1" t="n">
+        <v>46286.72618741898</v>
+      </c>
+      <c r="H1297" t="n">
+        <v>21.095</v>
+      </c>
+      <c r="I1297" t="n">
+        <v>2.810412347385393</v>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>NLMK</t>
+        </is>
+      </c>
+      <c r="C1298" t="n">
+        <v>71.64</v>
+      </c>
+      <c r="D1298" t="n">
+        <v>75.22200000000001</v>
+      </c>
+      <c r="E1298" t="n">
+        <v>68.05799999999999</v>
+      </c>
+      <c r="F1298" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1298" s="1" t="n">
+        <v>46286.72618741898</v>
+      </c>
+      <c r="H1298" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="I1298" t="n">
+        <v>2.149637074260198</v>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>MTSS</t>
+        </is>
+      </c>
+      <c r="C1299" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="D1299" t="n">
+        <v>209.895</v>
+      </c>
+      <c r="E1299" t="n">
+        <v>189.905</v>
+      </c>
+      <c r="F1299" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1299" s="1" t="n">
+        <v>46282.65388032408</v>
+      </c>
+      <c r="H1299" t="n">
+        <v>189.905</v>
+      </c>
+      <c r="I1299" t="n">
+        <v>5.000000000000003</v>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>MOEX</t>
+        </is>
+      </c>
+      <c r="C1300" t="n">
+        <v>152.19</v>
+      </c>
+      <c r="D1300" t="n">
+        <v>159.7995</v>
+      </c>
+      <c r="E1300" t="n">
+        <v>144.5805</v>
+      </c>
+      <c r="F1300" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1300" s="1" t="n">
+        <v>46286.72618741898</v>
+      </c>
+      <c r="H1300" t="n">
+        <v>146.81</v>
+      </c>
+      <c r="I1300" t="n">
+        <v>3.535054865628488</v>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="B1297" t="inlineStr">
+      <c r="B1301" t="inlineStr">
         <is>
           <t>MTSS</t>
         </is>
       </c>
-      <c r="C1297" t="n">
+      <c r="C1301" t="n">
         <v>185.15</v>
       </c>
-      <c r="D1297" t="n">
+      <c r="D1301" t="n">
         <v>194.4075</v>
       </c>
-      <c r="E1297" t="n">
+      <c r="E1301" t="n">
         <v>175.8925</v>
       </c>
-      <c r="F1297" t="inlineStr">
-        <is>
-          <t>Sell</t>
-        </is>
-      </c>
-      <c r="G1297" s="1" t="n">
-        <v>46283.63822962082</v>
-      </c>
-      <c r="H1297" t="n">
+      <c r="F1301" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1301" s="1" t="n">
+        <v>46283.63822961805</v>
+      </c>
+      <c r="H1301" t="n">
         <v>175.8925</v>
       </c>
-      <c r="I1297" t="n">
+      <c r="I1301" t="n">
         <v>4.999999999999996</v>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1302" t="n">
+        <v>5304</v>
+      </c>
+      <c r="D1302" t="n">
+        <v>5569.2</v>
+      </c>
+      <c r="E1302" t="n">
+        <v>5038.8</v>
+      </c>
+      <c r="F1302" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1302" s="1" t="n">
+        <v>46286.72618741898</v>
+      </c>
+      <c r="H1302" t="n">
+        <v>5022</v>
+      </c>
+      <c r="I1302" t="n">
+        <v>5.316742081447964</v>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1303" t="n">
+        <v>5320</v>
+      </c>
+      <c r="D1303" t="n">
+        <v>5586</v>
+      </c>
+      <c r="E1303" t="n">
+        <v>5054</v>
+      </c>
+      <c r="F1303" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1303" s="1" t="n">
+        <v>46286.72618741898</v>
+      </c>
+      <c r="H1303" t="n">
+        <v>5202</v>
+      </c>
+      <c r="I1303" t="n">
+        <v>2.218045112781955</v>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>ROSN</t>
+        </is>
+      </c>
+      <c r="C1304" t="n">
+        <v>355.2</v>
+      </c>
+      <c r="D1304" t="n">
+        <v>372.96</v>
+      </c>
+      <c r="E1304" t="n">
+        <v>337.44</v>
+      </c>
+      <c r="F1304" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1304" s="1" t="n">
+        <v>46286.72618741898</v>
+      </c>
+      <c r="H1304" t="n">
+        <v>359.95</v>
+      </c>
+      <c r="I1304" t="n">
+        <v>-1.337274774774775</v>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>GAZP</t>
+        </is>
+      </c>
+      <c r="C1305" t="n">
+        <v>92.93000000000001</v>
+      </c>
+      <c r="D1305" t="n">
+        <v>97.57650000000001</v>
+      </c>
+      <c r="E1305" t="n">
+        <v>88.2835</v>
+      </c>
+      <c r="F1305" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1305" s="1" t="n">
+        <v>46286.72618741898</v>
+      </c>
+      <c r="H1305" t="n">
+        <v>97.08</v>
+      </c>
+      <c r="I1305" t="n">
+        <v>-4.465726891208427</v>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1306" t="n">
+        <v>5155</v>
+      </c>
+      <c r="D1306" t="n">
+        <v>5412.75</v>
+      </c>
+      <c r="E1306" t="n">
+        <v>4897.25</v>
+      </c>
+      <c r="F1306" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1306" s="1" t="n">
+        <v>46286.72618741898</v>
+      </c>
+      <c r="H1306" t="n">
+        <v>5022</v>
+      </c>
+      <c r="I1306" t="n">
+        <v>2.580019398642095</v>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>MTSS</t>
+        </is>
+      </c>
+      <c r="C1307" t="n">
+        <v>175.9</v>
+      </c>
+      <c r="D1307" t="n">
+        <v>184.695</v>
+      </c>
+      <c r="E1307" t="n">
+        <v>167.105</v>
+      </c>
+      <c r="F1307" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1307" s="1" t="n">
+        <v>46286.72618741898</v>
+      </c>
+      <c r="H1307" t="n">
+        <v>172.75</v>
+      </c>
+      <c r="I1307" t="n">
+        <v>1.790790221716888</v>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1308" t="n">
+        <v>5206.5</v>
+      </c>
+      <c r="D1308" t="n">
+        <v>5466.825</v>
+      </c>
+      <c r="E1308" t="n">
+        <v>4946.175</v>
+      </c>
+      <c r="F1308" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1308" s="1" t="n">
+        <v>46286.72618741898</v>
+      </c>
+      <c r="H1308" t="n">
+        <v>5202</v>
+      </c>
+      <c r="I1308" t="n">
+        <v>0.08643042350907519</v>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1309" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="D1309" t="n">
+        <v>20.2125</v>
+      </c>
+      <c r="E1309" t="n">
+        <v>18.2875</v>
+      </c>
+      <c r="F1309" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1309" s="1" t="n">
+        <v>46286.72618741898</v>
+      </c>
+      <c r="H1309" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="I1309" t="n">
+        <v>1.090909090909095</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>AFLT</t>
+        </is>
+      </c>
+      <c r="C1310" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="D1310" t="n">
+        <v>33.684</v>
+      </c>
+      <c r="E1310" t="n">
+        <v>30.476</v>
+      </c>
+      <c r="F1310" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1310" s="1" t="n">
+        <v>46286.72618741898</v>
+      </c>
+      <c r="H1310" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="I1310" t="n">
+        <v>-0.06234413965088256</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>GAZP</t>
+        </is>
+      </c>
+      <c r="C1311" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="D1311" t="n">
+        <v>90.72499999999999</v>
+      </c>
+      <c r="E1311" t="n">
+        <v>103.14</v>
+      </c>
+      <c r="F1311" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1311" s="1" t="n">
+        <v>46289.65978608796</v>
+      </c>
+      <c r="H1311" t="n">
+        <v>101.28</v>
+      </c>
+      <c r="I1311" t="n">
+        <v>6.052356020942409</v>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1312" t="n">
+        <v>5093</v>
+      </c>
+      <c r="D1312" t="n">
+        <v>5347.650000000001</v>
+      </c>
+      <c r="E1312" t="n">
+        <v>4838.349999999999</v>
+      </c>
+      <c r="F1312" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1312" s="1" t="n">
+        <v>46289.65978608796</v>
+      </c>
+      <c r="H1312" t="n">
+        <v>5030</v>
+      </c>
+      <c r="I1312" t="n">
+        <v>1.23699194973493</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1313" t="n">
+        <v>5201.5</v>
+      </c>
+      <c r="D1313" t="n">
+        <v>5461.575</v>
+      </c>
+      <c r="E1313" t="n">
+        <v>4941.425</v>
+      </c>
+      <c r="F1313" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1313" s="1" t="n">
+        <v>46289.65978608796</v>
+      </c>
+      <c r="H1313" t="n">
+        <v>5392</v>
+      </c>
+      <c r="I1313" t="n">
+        <v>-3.662405075459002</v>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>AFLT</t>
+        </is>
+      </c>
+      <c r="C1314" t="n">
+        <v>32.39</v>
+      </c>
+      <c r="D1314" t="n">
+        <v>34.0095</v>
+      </c>
+      <c r="E1314" t="n">
+        <v>30.7705</v>
+      </c>
+      <c r="F1314" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1314" s="1" t="n">
+        <v>46289.65978608796</v>
+      </c>
+      <c r="H1314" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="I1314" t="n">
+        <v>-1.265822784810116</v>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>RTKM</t>
+        </is>
+      </c>
+      <c r="C1315" t="n">
+        <v>39.21</v>
+      </c>
+      <c r="D1315" t="n">
+        <v>41.1705</v>
+      </c>
+      <c r="E1315" t="n">
+        <v>37.2495</v>
+      </c>
+      <c r="F1315" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1315" s="1" t="n">
+        <v>46289.65978608796</v>
+      </c>
+      <c r="H1315" t="n">
+        <v>39.16</v>
+      </c>
+      <c r="I1315" t="n">
+        <v>0.1275184901810871</v>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>SNGSP</t>
+        </is>
+      </c>
+      <c r="C1316" t="n">
+        <v>40.405</v>
+      </c>
+      <c r="D1316" t="n">
+        <v>42.42525000000001</v>
+      </c>
+      <c r="E1316" t="n">
+        <v>38.38475</v>
+      </c>
+      <c r="F1316" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1316" s="1" t="n">
+        <v>46289.65978608796</v>
+      </c>
+      <c r="H1316" t="n">
+        <v>40.395</v>
+      </c>
+      <c r="I1316" t="n">
+        <v>0.02474941220145529</v>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1317" t="n">
+        <v>5043</v>
+      </c>
+      <c r="D1317" t="n">
+        <v>5295.150000000001</v>
+      </c>
+      <c r="E1317" t="n">
+        <v>4790.849999999999</v>
+      </c>
+      <c r="F1317" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1317" s="1" t="n">
+        <v>46290.66129192855</v>
+      </c>
+      <c r="H1317" t="n">
+        <v>5115</v>
+      </c>
+      <c r="I1317" t="n">
+        <v>-1.427721594289113</v>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1318" t="n">
+        <v>5207</v>
+      </c>
+      <c r="D1318" t="n">
+        <v>5467.35</v>
+      </c>
+      <c r="E1318" t="n">
+        <v>4946.65</v>
+      </c>
+      <c r="F1318" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1318" s="1" t="n">
+        <v>46290.66129192855</v>
+      </c>
+      <c r="H1318" t="n">
+        <v>5376.5</v>
+      </c>
+      <c r="I1318" t="n">
+        <v>-3.255233339734972</v>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>RTKM</t>
+        </is>
+      </c>
+      <c r="C1319" t="n">
+        <v>39.17</v>
+      </c>
+      <c r="D1319" t="n">
+        <v>41.1285</v>
+      </c>
+      <c r="E1319" t="n">
+        <v>37.2115</v>
+      </c>
+      <c r="F1319" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1319" s="1" t="n">
+        <v>46290.66129192855</v>
+      </c>
+      <c r="H1319" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="I1319" t="n">
+        <v>0.2552974214960465</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>RNFT</t>
+        </is>
+      </c>
+      <c r="C1320" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="D1320" t="n">
+        <v>88.515</v>
+      </c>
+      <c r="E1320" t="n">
+        <v>80.08499999999999</v>
+      </c>
+      <c r="F1320" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1320" s="1" t="n">
+        <v>46290.66129192855</v>
+      </c>
+      <c r="H1320" t="n">
+        <v>84.84999999999999</v>
+      </c>
+      <c r="I1320" t="n">
+        <v>-0.6524317912218235</v>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>GAZP</t>
+        </is>
+      </c>
+      <c r="C1321" t="n">
+        <v>97.41</v>
+      </c>
+      <c r="D1321" t="n">
+        <v>102.2805</v>
+      </c>
+      <c r="E1321" t="n">
+        <v>92.53949999999999</v>
+      </c>
+      <c r="F1321" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1321" s="1" t="n">
+        <v>46289.65978608796</v>
+      </c>
+      <c r="H1321" t="n">
+        <v>102.2805</v>
+      </c>
+      <c r="I1321" t="n">
+        <v>-5.000000000000007</v>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1322" t="n">
+        <v>22.21</v>
+      </c>
+      <c r="D1322" t="n">
+        <v>23.3205</v>
+      </c>
+      <c r="E1322" t="n">
+        <v>21.0995</v>
+      </c>
+      <c r="F1322" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1322" s="1" t="n">
+        <v>46290.66129192855</v>
+      </c>
+      <c r="H1322" t="n">
+        <v>21.0995</v>
+      </c>
+      <c r="I1322" t="n">
+        <v>5.000000000000008</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>AFKS</t>
+        </is>
+      </c>
+      <c r="C1323" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="D1323" t="n">
+        <v>7.8645</v>
+      </c>
+      <c r="E1323" t="n">
+        <v>7.1155</v>
+      </c>
+      <c r="F1323" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1323" s="1" t="n">
+        <v>46290.66129192855</v>
+      </c>
+      <c r="H1323" t="n">
+        <v>7.1155</v>
+      </c>
+      <c r="I1323" t="n">
+        <v>5.000000000000004</v>
       </c>
     </row>
   </sheetData>

--- a/data/weekly_report.xlsx
+++ b/data/weekly_report.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1323"/>
+  <dimension ref="A1:I1344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43886,7 +43886,7 @@
         </is>
       </c>
       <c r="G1317" s="1" t="n">
-        <v>46290.66129192855</v>
+        <v>46290.66129193287</v>
       </c>
       <c r="H1317" t="n">
         <v>5115</v>
@@ -43919,7 +43919,7 @@
         </is>
       </c>
       <c r="G1318" s="1" t="n">
-        <v>46290.66129192855</v>
+        <v>46290.66129193287</v>
       </c>
       <c r="H1318" t="n">
         <v>5376.5</v>
@@ -43952,7 +43952,7 @@
         </is>
       </c>
       <c r="G1319" s="1" t="n">
-        <v>46290.66129192855</v>
+        <v>46290.66129193287</v>
       </c>
       <c r="H1319" t="n">
         <v>39.07</v>
@@ -43985,7 +43985,7 @@
         </is>
       </c>
       <c r="G1320" s="1" t="n">
-        <v>46290.66129192855</v>
+        <v>46290.66129193287</v>
       </c>
       <c r="H1320" t="n">
         <v>84.84999999999999</v>
@@ -44033,31 +44033,31 @@
       </c>
       <c r="B1322" t="inlineStr">
         <is>
-          <t>MAGN</t>
+          <t>HYDR</t>
         </is>
       </c>
       <c r="C1322" t="n">
-        <v>22.21</v>
+        <v>0.3825</v>
       </c>
       <c r="D1322" t="n">
-        <v>23.3205</v>
+        <v>0.363375</v>
       </c>
       <c r="E1322" t="n">
-        <v>21.0995</v>
+        <v>0.4131</v>
       </c>
       <c r="F1322" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="G1322" s="1" t="n">
-        <v>46290.66129192855</v>
+        <v>46293.78092690972</v>
       </c>
       <c r="H1322" t="n">
-        <v>21.0995</v>
+        <v>0.3789</v>
       </c>
       <c r="I1322" t="n">
-        <v>5.000000000000008</v>
+        <v>-0.9411764705882332</v>
       </c>
     </row>
     <row r="1323">
@@ -44066,31 +44066,724 @@
       </c>
       <c r="B1323" t="inlineStr">
         <is>
+          <t>ROSN</t>
+        </is>
+      </c>
+      <c r="C1323" t="n">
+        <v>365.65</v>
+      </c>
+      <c r="D1323" t="n">
+        <v>347.3674999999999</v>
+      </c>
+      <c r="E1323" t="n">
+        <v>394.902</v>
+      </c>
+      <c r="F1323" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1323" s="1" t="n">
+        <v>46293.78092690972</v>
+      </c>
+      <c r="H1323" t="n">
+        <v>356.4</v>
+      </c>
+      <c r="I1323" t="n">
+        <v>-2.529741556132914</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>GAZP</t>
+        </is>
+      </c>
+      <c r="C1324" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="D1324" t="n">
+        <v>97.565</v>
+      </c>
+      <c r="E1324" t="n">
+        <v>110.916</v>
+      </c>
+      <c r="F1324" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1324" s="1" t="n">
+        <v>46293.78092690972</v>
+      </c>
+      <c r="H1324" t="n">
+        <v>98.29000000000001</v>
+      </c>
+      <c r="I1324" t="n">
+        <v>-4.294060370009733</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>OZON</t>
+        </is>
+      </c>
+      <c r="C1325" t="n">
+        <v>2955</v>
+      </c>
+      <c r="D1325" t="n">
+        <v>3102.75</v>
+      </c>
+      <c r="E1325" t="n">
+        <v>2807.25</v>
+      </c>
+      <c r="F1325" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1325" s="1" t="n">
+        <v>46293.78092690972</v>
+      </c>
+      <c r="H1325" t="n">
+        <v>2921.5</v>
+      </c>
+      <c r="I1325" t="n">
+        <v>1.133671742808799</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1326" t="n">
+        <v>22.21</v>
+      </c>
+      <c r="D1326" t="n">
+        <v>23.3205</v>
+      </c>
+      <c r="E1326" t="n">
+        <v>21.0995</v>
+      </c>
+      <c r="F1326" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1326" s="1" t="n">
+        <v>46290.66129193287</v>
+      </c>
+      <c r="H1326" t="n">
+        <v>21.0995</v>
+      </c>
+      <c r="I1326" t="n">
+        <v>5.000000000000008</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1327" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="D1327" t="n">
+        <v>20.979</v>
+      </c>
+      <c r="E1327" t="n">
+        <v>18.981</v>
+      </c>
+      <c r="F1327" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1327" s="1" t="n">
+        <v>46293.78092690972</v>
+      </c>
+      <c r="H1327" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="I1327" t="n">
+        <v>3.653653653653656</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>CHMF</t>
+        </is>
+      </c>
+      <c r="C1328" t="n">
+        <v>658.2</v>
+      </c>
+      <c r="D1328" t="n">
+        <v>691.1100000000001</v>
+      </c>
+      <c r="E1328" t="n">
+        <v>625.29</v>
+      </c>
+      <c r="F1328" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1328" s="1" t="n">
+        <v>46293.78092690972</v>
+      </c>
+      <c r="H1328" t="n">
+        <v>627</v>
+      </c>
+      <c r="I1328" t="n">
+        <v>4.740200546946224</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
           <t>AFKS</t>
         </is>
       </c>
-      <c r="C1323" t="n">
+      <c r="C1329" t="n">
         <v>7.49</v>
       </c>
-      <c r="D1323" t="n">
+      <c r="D1329" t="n">
         <v>7.8645</v>
       </c>
-      <c r="E1323" t="n">
+      <c r="E1329" t="n">
         <v>7.1155</v>
       </c>
-      <c r="F1323" t="inlineStr">
-        <is>
-          <t>Sell</t>
-        </is>
-      </c>
-      <c r="G1323" s="1" t="n">
-        <v>46290.66129192855</v>
-      </c>
-      <c r="H1323" t="n">
+      <c r="F1329" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1329" s="1" t="n">
+        <v>46290.66129193287</v>
+      </c>
+      <c r="H1329" t="n">
         <v>7.1155</v>
       </c>
-      <c r="I1323" t="n">
+      <c r="I1329" t="n">
         <v>5.000000000000004</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>OZON</t>
+        </is>
+      </c>
+      <c r="C1330" t="n">
+        <v>2997.5</v>
+      </c>
+      <c r="D1330" t="n">
+        <v>2847.625</v>
+      </c>
+      <c r="E1330" t="n">
+        <v>3237.3</v>
+      </c>
+      <c r="F1330" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1330" s="1" t="n">
+        <v>46293.78092690972</v>
+      </c>
+      <c r="H1330" t="n">
+        <v>2921.5</v>
+      </c>
+      <c r="I1330" t="n">
+        <v>-2.535446205170976</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>GMKN</t>
+        </is>
+      </c>
+      <c r="C1331" t="n">
+        <v>119.7</v>
+      </c>
+      <c r="D1331" t="n">
+        <v>125.685</v>
+      </c>
+      <c r="E1331" t="n">
+        <v>113.715</v>
+      </c>
+      <c r="F1331" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1331" s="1" t="n">
+        <v>46293.78092690972</v>
+      </c>
+      <c r="H1331" t="n">
+        <v>117.06</v>
+      </c>
+      <c r="I1331" t="n">
+        <v>2.205513784461153</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>RUAL</t>
+        </is>
+      </c>
+      <c r="C1332" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="D1332" t="n">
+        <v>24.8115</v>
+      </c>
+      <c r="E1332" t="n">
+        <v>22.4485</v>
+      </c>
+      <c r="F1332" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1332" s="1" t="n">
+        <v>46293.78092690972</v>
+      </c>
+      <c r="H1332" t="n">
+        <v>23.21</v>
+      </c>
+      <c r="I1332" t="n">
+        <v>1.777401608125257</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1333" t="n">
+        <v>5075</v>
+      </c>
+      <c r="D1333" t="n">
+        <v>5328.75</v>
+      </c>
+      <c r="E1333" t="n">
+        <v>4821.25</v>
+      </c>
+      <c r="F1333" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1333" s="1" t="n">
+        <v>46293.78092690972</v>
+      </c>
+      <c r="H1333" t="n">
+        <v>5035</v>
+      </c>
+      <c r="I1333" t="n">
+        <v>0.7881773399014778</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1334" t="n">
+        <v>5410</v>
+      </c>
+      <c r="D1334" t="n">
+        <v>5680.5</v>
+      </c>
+      <c r="E1334" t="n">
+        <v>5139.5</v>
+      </c>
+      <c r="F1334" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1334" s="1" t="n">
+        <v>46293.78092690972</v>
+      </c>
+      <c r="H1334" t="n">
+        <v>5306</v>
+      </c>
+      <c r="I1334" t="n">
+        <v>1.922365988909427</v>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1335" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="D1335" t="n">
+        <v>22.6275</v>
+      </c>
+      <c r="E1335" t="n">
+        <v>20.4725</v>
+      </c>
+      <c r="F1335" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1335" s="1" t="n">
+        <v>46293.78092690972</v>
+      </c>
+      <c r="H1335" t="n">
+        <v>20.355</v>
+      </c>
+      <c r="I1335" t="n">
+        <v>5.54524361948956</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1336" t="n">
+        <v>5385</v>
+      </c>
+      <c r="D1336" t="n">
+        <v>5654.25</v>
+      </c>
+      <c r="E1336" t="n">
+        <v>5115.75</v>
+      </c>
+      <c r="F1336" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1336" s="1" t="n">
+        <v>46296.73625504629</v>
+      </c>
+      <c r="H1336" t="n">
+        <v>5416</v>
+      </c>
+      <c r="I1336" t="n">
+        <v>-0.5756731662024142</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>AFKS</t>
+        </is>
+      </c>
+      <c r="C1337" t="n">
+        <v>7.161</v>
+      </c>
+      <c r="D1337" t="n">
+        <v>7.51905</v>
+      </c>
+      <c r="E1337" t="n">
+        <v>6.802949999999999</v>
+      </c>
+      <c r="F1337" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1337" s="1" t="n">
+        <v>46296.73625504629</v>
+      </c>
+      <c r="H1337" t="n">
+        <v>6.925</v>
+      </c>
+      <c r="I1337" t="n">
+        <v>3.295629102080712</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>NLMK</t>
+        </is>
+      </c>
+      <c r="C1338" t="n">
+        <v>69.12</v>
+      </c>
+      <c r="D1338" t="n">
+        <v>72.57600000000001</v>
+      </c>
+      <c r="E1338" t="n">
+        <v>65.664</v>
+      </c>
+      <c r="F1338" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1338" s="1" t="n">
+        <v>46296.73625504629</v>
+      </c>
+      <c r="H1338" t="n">
+        <v>68.04000000000001</v>
+      </c>
+      <c r="I1338" t="n">
+        <v>1.562499999999997</v>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1339" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="D1339" t="n">
+        <v>20.4435</v>
+      </c>
+      <c r="E1339" t="n">
+        <v>18.4965</v>
+      </c>
+      <c r="F1339" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1339" s="1" t="n">
+        <v>46294.71719436342</v>
+      </c>
+      <c r="H1339" t="n">
+        <v>18.4965</v>
+      </c>
+      <c r="I1339" t="n">
+        <v>4.999999999999989</v>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>SIBN</t>
+        </is>
+      </c>
+      <c r="C1340" t="n">
+        <v>555.95</v>
+      </c>
+      <c r="D1340" t="n">
+        <v>528.1525</v>
+      </c>
+      <c r="E1340" t="n">
+        <v>600.426</v>
+      </c>
+      <c r="F1340" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1340" s="1" t="n">
+        <v>46297.70854445756</v>
+      </c>
+      <c r="H1340" t="n">
+        <v>556.55</v>
+      </c>
+      <c r="I1340" t="n">
+        <v>0.1079233744041567</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>HYDR</t>
+        </is>
+      </c>
+      <c r="C1341" t="n">
+        <v>0.3738</v>
+      </c>
+      <c r="D1341" t="n">
+        <v>0.3924900000000001</v>
+      </c>
+      <c r="E1341" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="F1341" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1341" s="1" t="n">
+        <v>46297.70854445756</v>
+      </c>
+      <c r="H1341" t="n">
+        <v>0.3792</v>
+      </c>
+      <c r="I1341" t="n">
+        <v>-1.444622792937389</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1342" t="n">
+        <v>5311.5</v>
+      </c>
+      <c r="D1342" t="n">
+        <v>5577.075</v>
+      </c>
+      <c r="E1342" t="n">
+        <v>5045.925</v>
+      </c>
+      <c r="F1342" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1342" s="1" t="n">
+        <v>46297.70854445756</v>
+      </c>
+      <c r="H1342" t="n">
+        <v>5416</v>
+      </c>
+      <c r="I1342" t="n">
+        <v>-1.96742916313659</v>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1343" t="n">
+        <v>20.285</v>
+      </c>
+      <c r="D1343" t="n">
+        <v>21.29925</v>
+      </c>
+      <c r="E1343" t="n">
+        <v>19.27075</v>
+      </c>
+      <c r="F1343" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1343" s="1" t="n">
+        <v>46297.70854445756</v>
+      </c>
+      <c r="H1343" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="I1343" t="n">
+        <v>-0.3204338180921926</v>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1344" t="n">
+        <v>18.93</v>
+      </c>
+      <c r="D1344" t="n">
+        <v>19.8765</v>
+      </c>
+      <c r="E1344" t="n">
+        <v>17.9835</v>
+      </c>
+      <c r="F1344" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1344" s="1" t="n">
+        <v>46297.70854445756</v>
+      </c>
+      <c r="H1344" t="n">
+        <v>18.46</v>
+      </c>
+      <c r="I1344" t="n">
+        <v>2.482831484416264</v>
       </c>
     </row>
   </sheetData>

--- a/data/weekly_report.xlsx
+++ b/data/weekly_report.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1344"/>
+  <dimension ref="A1:I1369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44495,17 +44495,17 @@
       </c>
       <c r="B1336" t="inlineStr">
         <is>
-          <t>LKOH</t>
+          <t>PHOR</t>
         </is>
       </c>
       <c r="C1336" t="n">
-        <v>5385</v>
+        <v>5073</v>
       </c>
       <c r="D1336" t="n">
-        <v>5654.25</v>
+        <v>5326.650000000001</v>
       </c>
       <c r="E1336" t="n">
-        <v>5115.75</v>
+        <v>4819.349999999999</v>
       </c>
       <c r="F1336" t="inlineStr">
         <is>
@@ -44513,13 +44513,13 @@
         </is>
       </c>
       <c r="G1336" s="1" t="n">
-        <v>46296.73625504629</v>
+        <v>46300.80343163195</v>
       </c>
       <c r="H1336" t="n">
-        <v>5416</v>
+        <v>5221</v>
       </c>
       <c r="I1336" t="n">
-        <v>-0.5756731662024142</v>
+        <v>-2.917405874236152</v>
       </c>
     </row>
     <row r="1337">
@@ -44528,17 +44528,17 @@
       </c>
       <c r="B1337" t="inlineStr">
         <is>
-          <t>AFKS</t>
+          <t>LKOH</t>
         </is>
       </c>
       <c r="C1337" t="n">
-        <v>7.161</v>
+        <v>5385</v>
       </c>
       <c r="D1337" t="n">
-        <v>7.51905</v>
+        <v>5654.25</v>
       </c>
       <c r="E1337" t="n">
-        <v>6.802949999999999</v>
+        <v>5115.75</v>
       </c>
       <c r="F1337" t="inlineStr">
         <is>
@@ -44549,10 +44549,10 @@
         <v>46296.73625504629</v>
       </c>
       <c r="H1337" t="n">
-        <v>6.925</v>
+        <v>5416</v>
       </c>
       <c r="I1337" t="n">
-        <v>3.295629102080712</v>
+        <v>-0.5756731662024142</v>
       </c>
     </row>
     <row r="1338">
@@ -44561,17 +44561,17 @@
       </c>
       <c r="B1338" t="inlineStr">
         <is>
-          <t>NLMK</t>
+          <t>AFKS</t>
         </is>
       </c>
       <c r="C1338" t="n">
-        <v>69.12</v>
+        <v>7.161</v>
       </c>
       <c r="D1338" t="n">
-        <v>72.57600000000001</v>
+        <v>7.51905</v>
       </c>
       <c r="E1338" t="n">
-        <v>65.664</v>
+        <v>6.802949999999999</v>
       </c>
       <c r="F1338" t="inlineStr">
         <is>
@@ -44582,10 +44582,10 @@
         <v>46296.73625504629</v>
       </c>
       <c r="H1338" t="n">
-        <v>68.04000000000001</v>
+        <v>6.925</v>
       </c>
       <c r="I1338" t="n">
-        <v>1.562499999999997</v>
+        <v>3.295629102080712</v>
       </c>
     </row>
     <row r="1339">
@@ -44594,17 +44594,17 @@
       </c>
       <c r="B1339" t="inlineStr">
         <is>
-          <t>ALRS</t>
+          <t>NLMK</t>
         </is>
       </c>
       <c r="C1339" t="n">
-        <v>19.47</v>
+        <v>69.12</v>
       </c>
       <c r="D1339" t="n">
-        <v>20.4435</v>
+        <v>72.57600000000001</v>
       </c>
       <c r="E1339" t="n">
-        <v>18.4965</v>
+        <v>65.664</v>
       </c>
       <c r="F1339" t="inlineStr">
         <is>
@@ -44612,46 +44612,46 @@
         </is>
       </c>
       <c r="G1339" s="1" t="n">
-        <v>46294.71719436342</v>
+        <v>46296.73625504629</v>
       </c>
       <c r="H1339" t="n">
-        <v>18.4965</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="I1339" t="n">
-        <v>4.999999999999989</v>
+        <v>1.562499999999997</v>
       </c>
     </row>
     <row r="1340">
       <c r="A1340" s="1" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="B1340" t="inlineStr">
         <is>
-          <t>SIBN</t>
+          <t>ALRS</t>
         </is>
       </c>
       <c r="C1340" t="n">
-        <v>555.95</v>
+        <v>19.47</v>
       </c>
       <c r="D1340" t="n">
-        <v>528.1525</v>
+        <v>20.4435</v>
       </c>
       <c r="E1340" t="n">
-        <v>600.426</v>
+        <v>18.4965</v>
       </c>
       <c r="F1340" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="G1340" s="1" t="n">
-        <v>46297.70854445756</v>
+        <v>46294.71719436342</v>
       </c>
       <c r="H1340" t="n">
-        <v>556.55</v>
+        <v>18.4965</v>
       </c>
       <c r="I1340" t="n">
-        <v>0.1079233744041567</v>
+        <v>4.999999999999989</v>
       </c>
     </row>
     <row r="1341">
@@ -44660,31 +44660,31 @@
       </c>
       <c r="B1341" t="inlineStr">
         <is>
-          <t>HYDR</t>
+          <t>SIBN</t>
         </is>
       </c>
       <c r="C1341" t="n">
-        <v>0.3738</v>
+        <v>555.95</v>
       </c>
       <c r="D1341" t="n">
-        <v>0.3924900000000001</v>
+        <v>528.1525</v>
       </c>
       <c r="E1341" t="n">
-        <v>0.35511</v>
+        <v>600.426</v>
       </c>
       <c r="F1341" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="G1341" s="1" t="n">
-        <v>46297.70854445756</v>
+        <v>46297.70854445602</v>
       </c>
       <c r="H1341" t="n">
-        <v>0.3792</v>
+        <v>556.55</v>
       </c>
       <c r="I1341" t="n">
-        <v>-1.444622792937389</v>
+        <v>0.1079233744041567</v>
       </c>
     </row>
     <row r="1342">
@@ -44693,17 +44693,17 @@
       </c>
       <c r="B1342" t="inlineStr">
         <is>
-          <t>LKOH</t>
+          <t>HYDR</t>
         </is>
       </c>
       <c r="C1342" t="n">
-        <v>5311.5</v>
+        <v>0.3738</v>
       </c>
       <c r="D1342" t="n">
-        <v>5577.075</v>
+        <v>0.3924900000000001</v>
       </c>
       <c r="E1342" t="n">
-        <v>5045.925</v>
+        <v>0.35511</v>
       </c>
       <c r="F1342" t="inlineStr">
         <is>
@@ -44711,13 +44711,13 @@
         </is>
       </c>
       <c r="G1342" s="1" t="n">
-        <v>46297.70854445756</v>
+        <v>46297.70854445602</v>
       </c>
       <c r="H1342" t="n">
-        <v>5416</v>
+        <v>0.3792</v>
       </c>
       <c r="I1342" t="n">
-        <v>-1.96742916313659</v>
+        <v>-1.444622792937389</v>
       </c>
     </row>
     <row r="1343">
@@ -44726,17 +44726,17 @@
       </c>
       <c r="B1343" t="inlineStr">
         <is>
-          <t>MAGN</t>
+          <t>PHOR</t>
         </is>
       </c>
       <c r="C1343" t="n">
-        <v>20.285</v>
+        <v>5043</v>
       </c>
       <c r="D1343" t="n">
-        <v>21.29925</v>
+        <v>5295.150000000001</v>
       </c>
       <c r="E1343" t="n">
-        <v>19.27075</v>
+        <v>4790.849999999999</v>
       </c>
       <c r="F1343" t="inlineStr">
         <is>
@@ -44744,13 +44744,13 @@
         </is>
       </c>
       <c r="G1343" s="1" t="n">
-        <v>46297.70854445756</v>
+        <v>46300.80343163195</v>
       </c>
       <c r="H1343" t="n">
-        <v>20.35</v>
+        <v>5221</v>
       </c>
       <c r="I1343" t="n">
-        <v>-0.3204338180921926</v>
+        <v>-3.529645052548087</v>
       </c>
     </row>
     <row r="1344">
@@ -44759,31 +44759,856 @@
       </c>
       <c r="B1344" t="inlineStr">
         <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1344" t="n">
+        <v>5311.5</v>
+      </c>
+      <c r="D1344" t="n">
+        <v>5577.075</v>
+      </c>
+      <c r="E1344" t="n">
+        <v>5045.925</v>
+      </c>
+      <c r="F1344" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1344" s="1" t="n">
+        <v>46297.70854445602</v>
+      </c>
+      <c r="H1344" t="n">
+        <v>5416</v>
+      </c>
+      <c r="I1344" t="n">
+        <v>-1.96742916313659</v>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1345" t="n">
+        <v>20.285</v>
+      </c>
+      <c r="D1345" t="n">
+        <v>21.29925</v>
+      </c>
+      <c r="E1345" t="n">
+        <v>19.27075</v>
+      </c>
+      <c r="F1345" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1345" s="1" t="n">
+        <v>46297.70854445602</v>
+      </c>
+      <c r="H1345" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="I1345" t="n">
+        <v>-0.3204338180921926</v>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
           <t>ALRS</t>
         </is>
       </c>
-      <c r="C1344" t="n">
+      <c r="C1346" t="n">
         <v>18.93</v>
       </c>
-      <c r="D1344" t="n">
+      <c r="D1346" t="n">
         <v>19.8765</v>
       </c>
-      <c r="E1344" t="n">
+      <c r="E1346" t="n">
         <v>17.9835</v>
       </c>
-      <c r="F1344" t="inlineStr">
-        <is>
-          <t>Sell</t>
-        </is>
-      </c>
-      <c r="G1344" s="1" t="n">
-        <v>46297.70854445756</v>
-      </c>
-      <c r="H1344" t="n">
+      <c r="F1346" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1346" s="1" t="n">
+        <v>46297.70854445602</v>
+      </c>
+      <c r="H1346" t="n">
         <v>18.46</v>
       </c>
-      <c r="I1344" t="n">
+      <c r="I1346" t="n">
         <v>2.482831484416264</v>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1347" t="n">
+        <v>5010</v>
+      </c>
+      <c r="D1347" t="n">
+        <v>5260.5</v>
+      </c>
+      <c r="E1347" t="n">
+        <v>4759.5</v>
+      </c>
+      <c r="F1347" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1347" s="1" t="n">
+        <v>46300.80343163195</v>
+      </c>
+      <c r="H1347" t="n">
+        <v>5221</v>
+      </c>
+      <c r="I1347" t="n">
+        <v>-4.211576846307386</v>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>RUAL</t>
+        </is>
+      </c>
+      <c r="C1348" t="n">
+        <v>23.505</v>
+      </c>
+      <c r="D1348" t="n">
+        <v>24.68025</v>
+      </c>
+      <c r="E1348" t="n">
+        <v>22.32975</v>
+      </c>
+      <c r="F1348" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1348" s="1" t="n">
+        <v>46300.80343163195</v>
+      </c>
+      <c r="H1348" t="n">
+        <v>23.82</v>
+      </c>
+      <c r="I1348" t="n">
+        <v>-1.340140395660503</v>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1349" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="D1349" t="n">
+        <v>19.4985</v>
+      </c>
+      <c r="E1349" t="n">
+        <v>17.6415</v>
+      </c>
+      <c r="F1349" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1349" s="1" t="n">
+        <v>46300.80343163195</v>
+      </c>
+      <c r="H1349" t="n">
+        <v>19.42</v>
+      </c>
+      <c r="I1349" t="n">
+        <v>-4.577275175013471</v>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>NLMK</t>
+        </is>
+      </c>
+      <c r="C1350" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="D1350" t="n">
+        <v>72.13500000000001</v>
+      </c>
+      <c r="E1350" t="n">
+        <v>65.265</v>
+      </c>
+      <c r="F1350" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1350" s="1" t="n">
+        <v>46300.80343163195</v>
+      </c>
+      <c r="H1350" t="n">
+        <v>72.86</v>
+      </c>
+      <c r="I1350" t="n">
+        <v>-6.055312954876269</v>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1351" t="n">
+        <v>20.485</v>
+      </c>
+      <c r="D1351" t="n">
+        <v>21.50925</v>
+      </c>
+      <c r="E1351" t="n">
+        <v>19.46075</v>
+      </c>
+      <c r="F1351" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1351" s="1" t="n">
+        <v>46300.80343163195</v>
+      </c>
+      <c r="H1351" t="n">
+        <v>21.855</v>
+      </c>
+      <c r="I1351" t="n">
+        <v>-6.687820356358317</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>AFKS</t>
+        </is>
+      </c>
+      <c r="C1352" t="n">
+        <v>6.895</v>
+      </c>
+      <c r="D1352" t="n">
+        <v>7.23975</v>
+      </c>
+      <c r="E1352" t="n">
+        <v>6.550249999999999</v>
+      </c>
+      <c r="F1352" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1352" s="1" t="n">
+        <v>46300.80343163195</v>
+      </c>
+      <c r="H1352" t="n">
+        <v>7.034</v>
+      </c>
+      <c r="I1352" t="n">
+        <v>-2.015953589557654</v>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>SNGSP</t>
+        </is>
+      </c>
+      <c r="C1353" t="n">
+        <v>39.965</v>
+      </c>
+      <c r="D1353" t="n">
+        <v>41.96325</v>
+      </c>
+      <c r="E1353" t="n">
+        <v>37.96675</v>
+      </c>
+      <c r="F1353" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1353" s="1" t="n">
+        <v>46300.80343163195</v>
+      </c>
+      <c r="H1353" t="n">
+        <v>41.915</v>
+      </c>
+      <c r="I1353" t="n">
+        <v>-4.879269360690594</v>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>TRMK</t>
+        </is>
+      </c>
+      <c r="C1354" t="n">
+        <v>58</v>
+      </c>
+      <c r="D1354" t="n">
+        <v>60.90000000000001</v>
+      </c>
+      <c r="E1354" t="n">
+        <v>55.09999999999999</v>
+      </c>
+      <c r="F1354" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1354" s="1" t="n">
+        <v>46300.80343163195</v>
+      </c>
+      <c r="H1354" t="n">
+        <v>59.38</v>
+      </c>
+      <c r="I1354" t="n">
+        <v>-2.379310344827591</v>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>RTKM</t>
+        </is>
+      </c>
+      <c r="C1355" t="n">
+        <v>38.52</v>
+      </c>
+      <c r="D1355" t="n">
+        <v>40.44600000000001</v>
+      </c>
+      <c r="E1355" t="n">
+        <v>36.594</v>
+      </c>
+      <c r="F1355" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1355" s="1" t="n">
+        <v>46300.80343163195</v>
+      </c>
+      <c r="H1355" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="I1355" t="n">
+        <v>-3.322949117341625</v>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>SNGS</t>
+        </is>
+      </c>
+      <c r="C1356" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="D1356" t="n">
+        <v>15.792</v>
+      </c>
+      <c r="E1356" t="n">
+        <v>14.288</v>
+      </c>
+      <c r="F1356" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1356" s="1" t="n">
+        <v>46300.80343163195</v>
+      </c>
+      <c r="H1356" t="n">
+        <v>15.595</v>
+      </c>
+      <c r="I1356" t="n">
+        <v>-3.690159574468095</v>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1357" t="n">
+        <v>5070</v>
+      </c>
+      <c r="D1357" t="n">
+        <v>5323.5</v>
+      </c>
+      <c r="E1357" t="n">
+        <v>4816.5</v>
+      </c>
+      <c r="F1357" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1357" s="1" t="n">
+        <v>46303.74037909722</v>
+      </c>
+      <c r="H1357" t="n">
+        <v>5203</v>
+      </c>
+      <c r="I1357" t="n">
+        <v>-2.6232741617357</v>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1358" t="n">
+        <v>5428</v>
+      </c>
+      <c r="D1358" t="n">
+        <v>5699.400000000001</v>
+      </c>
+      <c r="E1358" t="n">
+        <v>5156.599999999999</v>
+      </c>
+      <c r="F1358" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1358" s="1" t="n">
+        <v>46303.74037909722</v>
+      </c>
+      <c r="H1358" t="n">
+        <v>5582.5</v>
+      </c>
+      <c r="I1358" t="n">
+        <v>-2.846352247605011</v>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1359" t="n">
+        <v>20.945</v>
+      </c>
+      <c r="D1359" t="n">
+        <v>21.99225</v>
+      </c>
+      <c r="E1359" t="n">
+        <v>19.89775</v>
+      </c>
+      <c r="F1359" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1359" s="1" t="n">
+        <v>46301.72307359954</v>
+      </c>
+      <c r="H1359" t="n">
+        <v>21.99225</v>
+      </c>
+      <c r="I1359" t="n">
+        <v>-4.999999999999991</v>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1360" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="D1360" t="n">
+        <v>19.845</v>
+      </c>
+      <c r="E1360" t="n">
+        <v>17.955</v>
+      </c>
+      <c r="F1360" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1360" s="1" t="n">
+        <v>46303.74037909722</v>
+      </c>
+      <c r="H1360" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="I1360" t="n">
+        <v>-0.9523809523809509</v>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>RTKM</t>
+        </is>
+      </c>
+      <c r="C1361" t="n">
+        <v>39.33</v>
+      </c>
+      <c r="D1361" t="n">
+        <v>41.2965</v>
+      </c>
+      <c r="E1361" t="n">
+        <v>37.36349999999999</v>
+      </c>
+      <c r="F1361" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1361" s="1" t="n">
+        <v>46303.74037909722</v>
+      </c>
+      <c r="H1361" t="n">
+        <v>39.95</v>
+      </c>
+      <c r="I1361" t="n">
+        <v>-1.576404780066119</v>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>SIBN</t>
+        </is>
+      </c>
+      <c r="C1362" t="n">
+        <v>573.6</v>
+      </c>
+      <c r="D1362" t="n">
+        <v>544.92</v>
+      </c>
+      <c r="E1362" t="n">
+        <v>619.4880000000001</v>
+      </c>
+      <c r="F1362" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1362" s="1" t="n">
+        <v>46304.7288209574</v>
+      </c>
+      <c r="H1362" t="n">
+        <v>587.1</v>
+      </c>
+      <c r="I1362" t="n">
+        <v>2.353556485355648</v>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>HYDR</t>
+        </is>
+      </c>
+      <c r="C1363" t="n">
+        <v>0.3856</v>
+      </c>
+      <c r="D1363" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="E1363" t="n">
+        <v>0.416448</v>
+      </c>
+      <c r="F1363" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1363" s="1" t="n">
+        <v>46304.7288209574</v>
+      </c>
+      <c r="H1363" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="I1363" t="n">
+        <v>1.322614107883816</v>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>VTBR</t>
+        </is>
+      </c>
+      <c r="C1364" t="n">
+        <v>54.305</v>
+      </c>
+      <c r="D1364" t="n">
+        <v>51.58975</v>
+      </c>
+      <c r="E1364" t="n">
+        <v>58.64940000000001</v>
+      </c>
+      <c r="F1364" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1364" s="1" t="n">
+        <v>46304.7288209574</v>
+      </c>
+      <c r="H1364" t="n">
+        <v>54.135</v>
+      </c>
+      <c r="I1364" t="n">
+        <v>-0.3130466807844613</v>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>AFLT</t>
+        </is>
+      </c>
+      <c r="C1365" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="D1365" t="n">
+        <v>35.49</v>
+      </c>
+      <c r="E1365" t="n">
+        <v>32.10999999999999</v>
+      </c>
+      <c r="F1365" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1365" s="1" t="n">
+        <v>46304.7288209574</v>
+      </c>
+      <c r="H1365" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="I1365" t="n">
+        <v>0.8284023668638877</v>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1366" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="D1366" t="n">
+        <v>20.265</v>
+      </c>
+      <c r="E1366" t="n">
+        <v>18.335</v>
+      </c>
+      <c r="F1366" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1366" s="1" t="n">
+        <v>46304.7288209574</v>
+      </c>
+      <c r="H1366" t="n">
+        <v>19.15</v>
+      </c>
+      <c r="I1366" t="n">
+        <v>0.7772020725388711</v>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>AFKS</t>
+        </is>
+      </c>
+      <c r="C1367" t="n">
+        <v>7.057</v>
+      </c>
+      <c r="D1367" t="n">
+        <v>7.40985</v>
+      </c>
+      <c r="E1367" t="n">
+        <v>6.70415</v>
+      </c>
+      <c r="F1367" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1367" s="1" t="n">
+        <v>46304.7288209574</v>
+      </c>
+      <c r="H1367" t="n">
+        <v>7.145</v>
+      </c>
+      <c r="I1367" t="n">
+        <v>-1.246988805441394</v>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>GAZP</t>
+        </is>
+      </c>
+      <c r="C1368" t="n">
+        <v>97.45999999999999</v>
+      </c>
+      <c r="D1368" t="n">
+        <v>102.333</v>
+      </c>
+      <c r="E1368" t="n">
+        <v>92.58699999999999</v>
+      </c>
+      <c r="F1368" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1368" s="1" t="n">
+        <v>46304.7288209574</v>
+      </c>
+      <c r="H1368" t="n">
+        <v>97.47</v>
+      </c>
+      <c r="I1368" t="n">
+        <v>-0.01026061974143763</v>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>GMKN</t>
+        </is>
+      </c>
+      <c r="C1369" t="n">
+        <v>119.36</v>
+      </c>
+      <c r="D1369" t="n">
+        <v>125.328</v>
+      </c>
+      <c r="E1369" t="n">
+        <v>113.392</v>
+      </c>
+      <c r="F1369" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1369" s="1" t="n">
+        <v>46304.7288209574</v>
+      </c>
+      <c r="H1369" t="n">
+        <v>115.02</v>
+      </c>
+      <c r="I1369" t="n">
+        <v>3.636058981233247</v>
       </c>
     </row>
   </sheetData>
